--- a/output/pdf_financials_xlsx/TSLV.xlsx
+++ b/output/pdf_financials_xlsx/TSLV.xlsx
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>17.485202</v>
+        <v>-17.485202</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>7.739386</v>
+        <v>-7.739386</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.479356</v>
+        <v>-5.479356</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.68419</v>
+        <v>-3.68419</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>17.485202</v>
+        <v>-17.485202</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>7.739386</v>
+        <v>-7.739386</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.479356</v>
+        <v>-5.479356</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.68419</v>
+        <v>-3.68419</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -965,16 +965,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>17.485202</v>
+        <v>-17.485202</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>7.739386</v>
+        <v>-7.739386</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.479356</v>
+        <v>-5.479356</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.68419</v>
+        <v>-3.68419</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-3.253035</v>
@@ -1035,16 +1035,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>124.8943</v>
+        <v>-124.8943</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>128.989767</v>
+        <v>-128.989767</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>136.9839</v>
+        <v>-136.9839</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>184.2095</v>
+        <v>-184.2095</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>17.485202</v>
+        <v>-17.485202</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7.739386</v>
+        <v>-7.739386</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.479356</v>
+        <v>-5.479356</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.68419</v>
+        <v>-3.68419</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>17.496401</v>
+        <v>-17.474003</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.751134</v>
+        <v>-7.727638</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.489867</v>
+        <v>-5.468845</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.694858</v>
+        <v>-3.673522</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1163,16 +1163,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -9615,16 +9615,16 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>17.485202</v>
+        <v>-17.485202</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>7.739386</v>
+        <v>-7.739386</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>5.479356</v>
+        <v>-5.479356</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>3.68419</v>
+        <v>-3.68419</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -9689,16 +9689,16 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>17.554433</v>
+        <v>-17.554433</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>7.663382</v>
+        <v>-7.663382</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>5.4998</v>
+        <v>-5.4998</v>
       </c>
       <c r="H156" s="5" t="n">
-        <v>3.65087</v>
+        <v>-3.65087</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="F178" s="5" t="n">
-        <v>7.663382</v>
+        <v>-7.663382</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>5.4998</v>
+        <v>-5.4998</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TSLV.xlsx
+++ b/output/pdf_financials_xlsx/TSLV.xlsx
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039291</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0424</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.032599</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1062,13 +1062,13 @@
         <v>-17.485202</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.739386</v>
+        <v>-7.700095</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.479356</v>
+        <v>-5.436956</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.68419</v>
+        <v>-3.651591</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1110,13 +1110,13 @@
         <v>-17.474003</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.727638</v>
+        <v>-7.688347</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.468845</v>
+        <v>-5.426445</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.673522</v>
+        <v>-3.640923</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1226,19 +1226,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.589858</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.553349</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.825589</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.171294</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.89584</v>
       </c>
     </row>
     <row r="35">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.589858</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.553349</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.825589</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.171294</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.89584</v>
       </c>
     </row>
     <row r="37">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.354186</v>
+        <v>0.764328</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.290225</v>
+        <v>0.736876</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.21861</v>
+        <v>0.393021</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.378239</v>
+        <v>0.206945</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.041428</v>
+        <v>0.145588</v>
       </c>
     </row>
     <row r="49">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">

--- a/output/pdf_financials_xlsx/TSLV.xlsx
+++ b/output/pdf_financials_xlsx/TSLV.xlsx
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.057574</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.057574</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-12.590743</v>
+        <v>-12.648317</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-6.976994</v>
@@ -8624,7 +8624,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>-0.057574</v>
       </c>
